--- a/data/trans_dic/P3A$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,54; 63,92</t>
+          <t>54,12; 63,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,65</t>
+          <t>31,08; 38,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,77; 50,82</t>
+          <t>44,79; 50,86</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,39; 57,63</t>
+          <t>47,8; 57,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,9; 33,74</t>
+          <t>26,0; 33,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,36; 45,3</t>
+          <t>38,7; 45,27</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 58,59</t>
+          <t>14,63; 58,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 32,05</t>
+          <t>20,86; 31,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,33; 49,5</t>
+          <t>15,53; 48,99</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,73; 54,57</t>
+          <t>47,43; 54,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,13; 27,99</t>
+          <t>11,77; 28,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 41,62</t>
+          <t>25,15; 41,42</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,37; 49,74</t>
+          <t>40,07; 49,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 21,21</t>
+          <t>13,75; 21,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,05; 30,78</t>
+          <t>22,24; 30,84</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,85</t>
+          <t>0,97; 6,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,91</t>
+          <t>8,14; 11,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,11</t>
+          <t>6,59; 9,96</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,3; 49,35</t>
+          <t>33,28; 49,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,01; 22,91</t>
+          <t>17,66; 22,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27,3; 35,12</t>
+          <t>28,42; 35,27</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>275528; 322919</t>
+          <t>273403; 321288</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>138591; 172693</t>
+          <t>138859; 172851</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>426236; 483769</t>
+          <t>426355; 484205</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>214075; 260328</t>
+          <t>215924; 257682</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99106; 129067</t>
+          <t>99474; 129229</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>320022; 377918</t>
+          <t>322873; 377666</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88350; 391529</t>
+          <t>97754; 394221</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>35469; 53308</t>
+          <t>34708; 52984</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119561; 413161</t>
+          <t>129610; 408863</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>493957; 564752</t>
+          <t>490777; 563866</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>108909; 273785</t>
+          <t>115126; 275424</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>543357; 837687</t>
+          <t>506191; 833683</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>191799; 236293</t>
+          <t>190366; 236558</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>113166; 178440</t>
+          <t>115670; 180429</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>303432; 405244</t>
+          <t>292821; 405993</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2479; 16475</t>
+          <t>2325; 15714</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62556; 90712</t>
+          <t>62013; 91263</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>66772; 101308</t>
+          <t>65979; 99808</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1191427; 1665912</t>
+          <t>1123440; 1670693</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>608199; 819252</t>
+          <t>631486; 821798</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1897716; 2441300</t>
+          <t>1976122; 2452334</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$pareja-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>54,12; 63,59</t>
+          <t>54,44; 63,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,08; 38,69</t>
+          <t>30,73; 37,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,79; 50,86</t>
+          <t>44,32; 50,41</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,8; 57,04</t>
+          <t>48,14; 57,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,0; 33,78</t>
+          <t>24,48; 32,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38,7; 45,27</t>
+          <t>38,26; 44,67</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,63; 58,99</t>
+          <t>52,94; 62,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,86; 31,85</t>
+          <t>21,04; 31,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,53; 48,99</t>
+          <t>44,69; 52,39</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>47,43; 54,49</t>
+          <t>49,08; 55,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,77; 28,16</t>
+          <t>24,01; 29,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,15; 41,42</t>
+          <t>38,83; 43,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,07; 49,8</t>
+          <t>40,56; 49,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 21,45</t>
+          <t>17,79; 22,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,24; 30,84</t>
+          <t>27,6; 32,3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,53</t>
+          <t>1,26; 7,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,99</t>
+          <t>7,91; 11,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,59; 9,96</t>
+          <t>6,95; 9,96</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>35,56%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,28; 49,49</t>
+          <t>47,58; 51,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,66; 22,98</t>
+          <t>21,09; 23,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28,42; 35,27</t>
+          <t>34,47; 36,75</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>299159</t>
+          <t>327450</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>155564</t>
+          <t>166828</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>454723</t>
+          <t>494278</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>273403; 321288</t>
+          <t>299737; 350385</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>138859; 172851</t>
+          <t>149877; 185151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>426355; 484205</t>
+          <t>460187; 523385</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>236580</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>113162</t>
+          <t>120515</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>349742</t>
+          <t>375987</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>215924; 257682</t>
+          <t>232385; 277038</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>99474; 129229</t>
+          <t>103598; 137272</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>322873; 377666</t>
+          <t>346623; 404680</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>271032</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>285029</t>
+          <t>318728</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97754; 394221</t>
+          <t>249655; 294528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34708; 52984</t>
+          <t>39326; 59592</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129610; 408863</t>
+          <t>294290; 345018</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>528324</t>
+          <t>587623</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>210081</t>
+          <t>230379</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>738405</t>
+          <t>818001</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>490777; 563866</t>
+          <t>555509; 624355</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115126; 275424</t>
+          <t>206784; 253266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>506191; 833683</t>
+          <t>773834; 860512</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>213741</t>
+          <t>254400</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>152338</t>
+          <t>164940</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366078</t>
+          <t>419340</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>190366; 236558</t>
+          <t>230392; 280426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>115670; 180429</t>
+          <t>147780; 186615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>292821; 405993</t>
+          <t>386066; 451832</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>81922</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82592</t>
+          <t>89646</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2325; 15714</t>
+          <t>2996; 17561</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62013; 91263</t>
+          <t>66775; 98547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>65979; 99808</t>
+          <t>75208; 107732</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1526795</t>
+          <t>1703701</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>749774</t>
+          <t>812281</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2276569</t>
+          <t>2515981</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1123440; 1670693</t>
+          <t>1637696; 1766642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>631486; 821798</t>
+          <t>766426; 853049</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1976122; 2452334</t>
+          <t>2439039; 2600231</t>
         </is>
       </c>
     </row>
